--- a/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · Dido y Eneas</t>
   </si>
   <si>
-    <t>Para Gaston Gilabert · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Gaston Gilabert · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="327">
   <si>
     <t>Migración métrica · Dido y Eneas</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -60,9 +60,6 @@
     <t>lista</t>
   </si>
   <si>
-    <t>Sí, es un mismo pasaje</t>
-  </si>
-  <si>
     <t>Abrazada · abba</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>Es correcto</t>
   </si>
   <si>
-    <t>No, son pasajes distintos</t>
-  </si>
-  <si>
     <t>Cruzada · abab</t>
   </si>
   <si>
@@ -132,7 +126,7 @@
     <t>Clave</t>
   </si>
   <si>
-    <t>Decidir</t>
+    <t>Responder</t>
   </si>
   <si>
     <t>169–378</t>
@@ -141,27 +135,21 @@
     <t>Sexteto-lira · Heterométrico consonante</t>
   </si>
   <si>
-    <t>En tu obra este pasaje está dividido en 4 secuencias (169–174, 175–180, 181–186, 187–378). En el modelo nuevo pasa a ser una sola, con 35 estrofas de 6 versos, y lo que distinguía a cada parte se conserva en sus estrofas. ¿Es realmente un mismo pasaje?</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>F|427f8f00-401d-41d6-9cba-dda5de6c0560|5fbaed87-05a8-499c-a768-417df99b2dd8</t>
-  </si>
-  <si>
-    <t>Responder</t>
-  </si>
-  <si>
     <t>Escribe la sinopsis de la secuencia completa</t>
   </si>
   <si>
-    <t xml:space="preserve">La acción se traslada a Troya durante su destrucción. Eneas sale armado en medio del incendio y comprende que la ciudad, que no pudo ser vencida por la fuerza, ha caído por el engaño de los griegos. Recuerda entonces que las profecías de Casandra eran ciertas y maldice a Sinón, responsable de convencer a los troyanos para que introdujeran el caballo dentro de las murallas. Eneas contempla cómo las armas griegas siembran la muerte por Troya mientras el incendio se extiende por los edificios. Las llamas alcanzan tal altura que parecen abrasar el cielo y, al mismo tiempo, iluminan toda la tierra. Eneas lamenta la desgracia de Troya y declara que los griegos han consumado su venganza entre los gritos y gemidos de la población. Al oír que desde dentro siguen clamando «¡Fuego!», maldice a Elena y desea que arda, pues su rapto fue la causa de la guerra. Eneas desea defender Troya y morir combatiendo, pero Acates le hace ver que la ciudad está irremediablemente perdida. Le describe la matanza provocada por los griegos que salieron del caballo: Pirro ha decapitado a Príamo, ha degollado a Hécuba y ha sacrificado a Políxena en el templo; el palacio real ha quedado reducido a escombros y sepulta a vivos y muertos. También contemplan cómo Corebo intenta rescatar a Casandra, apresada por los enemigos.
+    <t xml:space="preserve">La acción se traslada a Troya durante su destrucción. Eneas sale armado en medio del incendio y comprende que la ciudad, que no pudo ser vencida por la fuerza, ha caído por el engaño de los griegos. Recuerda entonces que las profecías de Casandra eran ciertas y maldice a Sinón, responsable de convencer a los troyanos para que introdujeran el caballo dentro de las murallas.
+Eneas contempla cómo las armas griegas siembran la muerte por Troya mientras el incendio se extiende por los edificios. Las llamas alcanzan tal altura que parecen abrasar el cielo y, al mismo tiempo, iluminan toda la tierra.
+Eneas lamenta la desgracia de Troya y declara que los griegos han consumado su venganza entre los gritos y gemidos de la población. Al oír que desde dentro siguen clamando «¡Fuego!», maldice a Elena y desea que arda, pues su rapto fue la causa de la guerra.
+Eneas desea defender Troya y morir combatiendo, pero Acates le hace ver que la ciudad está irremediablemente perdida. Le describe la matanza provocada por los griegos que salieron del caballo: Pirro ha decapitado a Príamo, ha degollado a Hécuba y ha sacrificado a Políxena en el templo; el palacio real ha quedado reducido a escombros y sepulta a vivos y muertos. También contemplan cómo Corebo intenta rescatar a Casandra, apresada por los enemigos.
 Ante los gritos de victoria de los griegos, Eneas llama a los troyanos a resistir y se enfrenta a Pirro. Aunque consigue hacer retroceder a parte de los atacantes, Acates le advierte de que su valor individual no puede salvar la ciudad y le señala su propia casa, envuelta en llamas. Allí están atrapados su padre Anquises, su hijo Ascanio y su esposa Creúsa. Eneas deja el combate y acude a rescatarlos. Anquises le pide que salve primero a Creúsa y al niño, pero Eneas decide cargar antes con su anciano padre.
 Eneas huye llevando a Anquises sobre los hombros, a Ascanio de la mano y seguido por Creúsa, mientras Pirro y sus hombres los persiguen. En la confusión, Creúsa desaparece. Eneas deja a su padre y a su hijo junto al templo de Ceres y regresa solo a buscarla, dispuesto incluso a morir. Finalmente se le aparece la sombra ensangrentada de Creúsa y le comunica que ha muerto. Le ordena que abandone su búsqueda, siga su destino errante hasta el reino latino y cuide de Ascanio. Allí triunfará y recibirá otra esposa. Eneas intenta retenerla y abrazarla, pero Creúsa desaparece definitivamente, pues ya no es más que una sombra.</t>
   </si>
   <si>
-    <t>En «Propuesta» tienes las 4 sinopsis actuales, una detrás de otra, para partir de ellas</t>
+    <t>En «Propuesta» tienes las 4 sinopsis actuales del tramo, en párrafos separados, para partir de ellas</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>S|427f8f00-401d-41d6-9cba-dda5de6c0560</t>
@@ -362,10 +350,214 @@
     <t>2053–2227</t>
   </si>
   <si>
-    <t>Esquema de rima · 35 estrofas</t>
-  </si>
-  <si>
-    <t>R|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
+    <t>Esquema de rima · estrofa 1 (vv. 2053–2057)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2053</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 2 (vv. 2058–2062)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2058</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 3 (vv. 2063–2067)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2063</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 4 (vv. 2068–2072)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2068</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 5 (vv. 2073–2077)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2073</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 6 (vv. 2078–2082)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2078</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 7 (vv. 2083–2087)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2083</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 8 (vv. 2088–2092)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2088</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 9 (vv. 2093–2097)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2093</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 10 (vv. 2098–2102)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2098</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 11 (vv. 2103–2107)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2103</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 12 (vv. 2108–2112)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2108</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 13 (vv. 2113–2117)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2113</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 14 (vv. 2118–2122)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2118</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 15 (vv. 2123–2127)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2123</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 16 (vv. 2128–2132)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2128</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 17 (vv. 2133–2137)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2133</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 18 (vv. 2138–2142)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2138</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 19 (vv. 2143–2147)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2143</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 20 (vv. 2148–2152)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2148</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 21 (vv. 2153–2157)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2153</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 22 (vv. 2158–2162)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2158</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 23 (vv. 2163–2167)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2163</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 24 (vv. 2168–2172)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2168</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 25 (vv. 2173–2177)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2173</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 26 (vv. 2178–2182)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2178</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 27 (vv. 2183–2187)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2183</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 28 (vv. 2188–2192)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2188</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 29 (vv. 2193–2197)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2193</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 30 (vv. 2198–2202)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2198</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 31 (vv. 2203–2207)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2203</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 32 (vv. 2208–2212)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2208</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 33 (vv. 2213–2217)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2213</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 34 (vv. 2218–2222)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2218</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 35 (vv. 2223–2227)</t>
+  </si>
+  <si>
+    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2223</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -413,6 +605,18 @@
     <t>C|427f8f00-401d-41d6-9cba-dda5de6c0560</t>
   </si>
   <si>
+    <t>Un solo pasaje</t>
+  </si>
+  <si>
+    <t>En tu obra este pasaje está dividido en 4 secuencias (169–174, 175–180, 181–186, 187–378), y pasa a ser una sola con 35 estrofas de 6 versos: lo que distinguía a cada parte se conserva en sus estrofas.</t>
+  </si>
+  <si>
+    <t>sexteto_lira_a2_AbaBcC, sexteto_lira_a1_aBaBcC, sexteto_lira_a3_abaBcC</t>
+  </si>
+  <si>
+    <t>F|427f8f00-401d-41d6-9cba-dda5de6c0560|5fbaed87-05a8-499c-a768-417df99b2dd8</t>
+  </si>
+  <si>
     <t>175–180</t>
   </si>
   <si>
@@ -593,7 +797,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>Sílabas (opcional)</t>
@@ -614,7 +818,7 @@
     <t>D|1213f60e-b47c-40be-bc40-6dbf5f7cdc3d</t>
   </si>
   <si>
-    <t>Informativa</t>
+    <t>Revisar</t>
   </si>
   <si>
     <t>1626</t>
@@ -1304,13 +1508,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="40" customWidth="1"/>
+    <col min="1" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1320,11 +1524,8 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1334,52 +1535,46 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1406,54 +1601,54 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>42</v>
@@ -1470,19 +1665,19 @@
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>47</v>
@@ -1502,54 +1697,54 @@
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>42</v>
@@ -1566,86 +1761,86 @@
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>42</v>
@@ -1657,27 +1852,27 @@
         <v>42</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>42</v>
@@ -1689,27 +1884,27 @@
         <v>42</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>42</v>
@@ -1721,27 +1916,27 @@
         <v>42</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>42</v>
@@ -1753,27 +1948,27 @@
         <v>42</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>42</v>
@@ -1785,27 +1980,27 @@
         <v>42</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>42</v>
@@ -1817,27 +2012,27 @@
         <v>42</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>42</v>
@@ -1849,27 +2044,27 @@
         <v>42</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>42</v>
@@ -1881,27 +2076,27 @@
         <v>42</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>42</v>
@@ -1913,27 +2108,27 @@
         <v>42</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>42</v>
@@ -1945,27 +2140,27 @@
         <v>42</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>42</v>
@@ -1977,27 +2172,27 @@
         <v>42</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>42</v>
@@ -2009,27 +2204,27 @@
         <v>42</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>42</v>
@@ -2041,27 +2236,27 @@
         <v>42</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>42</v>
@@ -2073,27 +2268,27 @@
         <v>42</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>42</v>
@@ -2105,27 +2300,27 @@
         <v>42</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>42</v>
@@ -2137,27 +2332,27 @@
         <v>42</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>42</v>
@@ -2169,27 +2364,27 @@
         <v>42</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>42</v>
@@ -2201,27 +2396,27 @@
         <v>42</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>42</v>
@@ -2233,27 +2428,27 @@
         <v>42</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>42</v>
@@ -2265,27 +2460,27 @@
         <v>42</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>42</v>
@@ -2297,27 +2492,27 @@
         <v>42</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>42</v>
@@ -2329,27 +2524,27 @@
         <v>42</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>42</v>
@@ -2361,27 +2556,27 @@
         <v>42</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>42</v>
@@ -2393,55 +2588,1108 @@
         <v>42</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="7" t="s">
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>115</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G32">
-      <formula1>Listas!$C$2:$C$9</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G65">
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3:G4">
       <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G5">
-      <formula1>Listas!$B$2:$B$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G32">
-      <formula1>Listas!$C$2:$C$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G65">
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2451,7 +3699,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2467,48 +3715,48 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>42</v>
@@ -2520,24 +3768,24 @@
         <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>125</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>42</v>
@@ -2549,24 +3797,24 @@
         <v>42</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>42</v>
@@ -2578,24 +3826,24 @@
         <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>42</v>
@@ -2607,24 +3855,24 @@
         <v>42</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>138</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>139</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>42</v>
@@ -2636,24 +3884,24 @@
         <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>42</v>
@@ -2665,24 +3913,24 @@
         <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>147</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>42</v>
@@ -2694,24 +3942,24 @@
         <v>42</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>42</v>
@@ -2723,24 +3971,24 @@
         <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>42</v>
@@ -2752,24 +4000,24 @@
         <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>42</v>
@@ -2781,24 +4029,24 @@
         <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>42</v>
@@ -2810,24 +4058,24 @@
         <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>42</v>
@@ -2839,24 +4087,24 @@
         <v>42</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
@@ -2868,24 +4116,24 @@
         <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>42</v>
@@ -2897,24 +4145,24 @@
         <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>177</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>178</v>
+        <v>242</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>42</v>
@@ -2926,24 +4174,24 @@
         <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>211</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>42</v>
@@ -2955,24 +4203,24 @@
         <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>153</v>
+        <v>250</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>42</v>
@@ -2984,17 +4232,46 @@
         <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>186</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F18">
-      <formula1>Listas!$D$2:$D$3</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F19">
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F18">
-      <formula1>Listas!$D$2:$D$3</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F19">
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3013,7 +4290,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -3021,54 +4298,54 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>187</v>
+        <v>254</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>42</v>
@@ -3080,27 +4357,27 @@
         <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>42</v>
@@ -3112,27 +4389,27 @@
         <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>42</v>
@@ -3144,27 +4421,27 @@
         <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>207</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>42</v>
@@ -3176,27 +4453,27 @@
         <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>42</v>
@@ -3208,27 +4485,27 @@
         <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>42</v>
@@ -3240,27 +4517,27 @@
         <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>42</v>
@@ -3272,11 +4549,16 @@
         <v>42</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H8">
+      <formula1>Listas!$C$2:$C$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3302,37 +4584,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>225</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3340,34 +4622,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3">
         <v>168</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3375,34 +4657,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3410,34 +4692,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3445,34 +4727,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3480,34 +4762,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3">
         <v>192</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>234</v>
+        <v>301</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>235</v>
+        <v>302</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3515,34 +4797,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="C7" s="3">
         <v>164</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3550,34 +4832,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3">
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3585,34 +4867,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="C9" s="3">
         <v>148</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3620,34 +4902,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3">
         <v>172</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3655,34 +4937,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3">
         <v>102</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3690,34 +4972,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3">
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3725,34 +5007,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="C13" s="3">
         <v>128</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3760,34 +5042,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3795,34 +5077,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="C15" s="3">
         <v>192</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3830,34 +5112,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="C16" s="3">
         <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>248</v>
+        <v>315</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3865,34 +5147,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="C17" s="3">
         <v>224</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3900,34 +5182,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="C18" s="3">
         <v>78</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>254</v>
+        <v>321</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3935,34 +5217,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="C19" s="3">
         <v>176</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3970,34 +5252,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3">
         <v>175</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4005,34 +5287,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="C21" s="3">
         <v>154</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4040,34 +5322,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="C22" s="3">
         <v>472</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4075,34 +5357,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="C23" s="3">
         <v>118</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4110,34 +5392,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="C24" s="3">
         <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4145,34 +5427,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="C25" s="3">
         <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
@@ -21,7 +21,7 @@
     <t>Migración métrica · Dido y Eneas</t>
   </si>
   <si>
-    <t>Para Gaston Gilabert · generado el 2026-09-20</t>
+    <t>Para Gaston Gilabert · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="210">
   <si>
     <t>Migración métrica · Dido y Eneas</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -164,7 +164,7 @@
     <t>Esquema de rima · 20 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
   </si>
   <si>
     <t>R|5f98abeb-2033-4a53-9707-17d68b216e1d|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -185,379 +185,28 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1045–1049)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1045</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1050–1054)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1050</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1055–1059)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1055</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1060–1064)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1060</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1065–1069)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1065</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1070–1074)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1070</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1075–1079)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1075</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1080–1084)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1080</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 1085–1089)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1085</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 1090–1094)</t>
-  </si>
-  <si>
-    <t>U|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066|1090</t>
+    <t>Esquema de rima · 10 estrofas</t>
+  </si>
+  <si>
+    <t>R|f1700144-7974-4f12-9210-bdbfce6a133e|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>1223–1302</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1223–1227)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1223</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1228–1232)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1228</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1233–1237)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1233</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1238–1242)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1238</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1243–1247)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1243</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1248–1252)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1248</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1253–1257)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1253</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1258–1262)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1258</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 1263–1267)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1263</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 1268–1272)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1268</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 1273–1277)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1273</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 1278–1282)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1278</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 1283–1287)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1283</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 1288–1292)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1288</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 1293–1297)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1293</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 1298–1302)</t>
-  </si>
-  <si>
-    <t>U|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066|1298</t>
+    <t>Esquema de rima · 16 estrofas</t>
+  </si>
+  <si>
+    <t>R|63431d5f-e003-496f-acf2-fc34de2c41fa|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>2053–2227</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 2053–2057)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2053</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 2058–2062)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2058</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 2063–2067)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2063</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 2068–2072)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2068</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 2073–2077)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2073</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 2078–2082)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2078</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 2083–2087)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2083</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 2088–2092)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2088</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 2093–2097)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2093</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 2098–2102)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2098</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 2103–2107)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2103</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 2108–2112)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2108</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 2113–2117)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2113</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 2118–2122)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2118</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 2123–2127)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2123</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 2128–2132)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2128</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 17 (vv. 2133–2137)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2133</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 18 (vv. 2138–2142)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2138</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 19 (vv. 2143–2147)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2143</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 20 (vv. 2148–2152)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2148</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 21 (vv. 2153–2157)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2153</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 22 (vv. 2158–2162)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2158</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 23 (vv. 2163–2167)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2163</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 24 (vv. 2168–2172)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2168</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 25 (vv. 2173–2177)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2173</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 26 (vv. 2178–2182)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2178</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 27 (vv. 2183–2187)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2183</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 28 (vv. 2188–2192)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2188</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 29 (vv. 2193–2197)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2193</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 30 (vv. 2198–2202)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2198</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 31 (vv. 2203–2207)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2203</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 32 (vv. 2208–2212)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2208</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 33 (vv. 2213–2217)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2213</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 34 (vv. 2218–2222)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2218</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 35 (vv. 2223–2227)</t>
-  </si>
-  <si>
-    <t>U|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066|2223</t>
+    <t>Esquema de rima · 35 estrofas</t>
+  </si>
+  <si>
+    <t>R|b39356d5-0bdc-4137-b17f-78e9af027093|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -590,10 +239,22 @@
     <t>C|3cae4df4-a392-480e-8754-2b27a0970278</t>
   </si>
   <si>
+    <t>Un solo pasaje</t>
+  </si>
+  <si>
+    <t>En tu obra este pasaje está dividido en 4 secuencias (169–174, 175–180, 181–186, 187–378), y pasa a ser una sola con 35 estrofas de 6 versos: lo que distinguía a cada parte se conserva en sus estrofas.</t>
+  </si>
+  <si>
+    <t>sexteto_lira_a2_AbaBcC, sexteto_lira_a1_aBaBcC, sexteto_lira_a3_abaBcC</t>
+  </si>
+  <si>
+    <t>F|427f8f00-401d-41d6-9cba-dda5de6c0560|5fbaed87-05a8-499c-a768-417df99b2dd8</t>
+  </si>
+  <si>
     <t>169–174</t>
   </si>
   <si>
-    <t>Variedad</t>
+    <t>Variedad · dentro del pasaje 169–378</t>
   </si>
   <si>
     <t>A2 · AbaBcC</t>
@@ -603,18 +264,6 @@
   </si>
   <si>
     <t>C|427f8f00-401d-41d6-9cba-dda5de6c0560</t>
-  </si>
-  <si>
-    <t>Un solo pasaje</t>
-  </si>
-  <si>
-    <t>En tu obra este pasaje está dividido en 4 secuencias (169–174, 175–180, 181–186, 187–378), y pasa a ser una sola con 35 estrofas de 6 versos: lo que distinguía a cada parte se conserva en sus estrofas.</t>
-  </si>
-  <si>
-    <t>sexteto_lira_a2_AbaBcC, sexteto_lira_a1_aBaBcC, sexteto_lira_a3_abaBcC</t>
-  </si>
-  <si>
-    <t>F|427f8f00-401d-41d6-9cba-dda5de6c0560|5fbaed87-05a8-499c-a768-417df99b2dd8</t>
   </si>
   <si>
     <t>175–180</t>
@@ -1585,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1744,19 +1393,19 @@
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1764,7 +1413,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>53</v>
@@ -1776,7 +1425,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>42</v>
@@ -1796,19 +1445,19 @@
         <v>36</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>42</v>
@@ -1820,1875 +1469,16 @@
         <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G65">
-      <formula1>Listas!$B$2:$B$9</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3:G4">
       <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G65">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G7">
       <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -3721,19 +1511,19 @@
         <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>34</v>
@@ -3744,19 +1534,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>42</v>
@@ -3768,24 +1558,24 @@
         <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>189</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>42</v>
@@ -3797,24 +1587,24 @@
         <v>42</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>42</v>
@@ -3826,24 +1616,24 @@
         <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>42</v>
@@ -3855,24 +1645,24 @@
         <v>42</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>42</v>
@@ -3884,24 +1674,24 @@
         <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>42</v>
@@ -3913,24 +1703,24 @@
         <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>42</v>
@@ -3942,24 +1732,24 @@
         <v>42</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>214</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>42</v>
@@ -3971,24 +1761,24 @@
         <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>42</v>
@@ -4000,24 +1790,24 @@
         <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>42</v>
@@ -4029,24 +1819,24 @@
         <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>42</v>
@@ -4058,24 +1848,24 @@
         <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>230</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>42</v>
@@ -4087,24 +1877,24 @@
         <v>42</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
@@ -4116,24 +1906,24 @@
         <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>239</v>
+        <v>122</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>42</v>
@@ -4145,24 +1935,24 @@
         <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>42</v>
@@ -4174,24 +1964,24 @@
         <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>42</v>
@@ -4203,24 +1993,24 @@
         <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>248</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>42</v>
@@ -4232,24 +2022,24 @@
         <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>251</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>42</v>
@@ -4261,7 +2051,7 @@
         <v>42</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>253</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -4304,22 +2094,22 @@
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>254</v>
+        <v>137</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>257</v>
+        <v>140</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>34</v>
@@ -4330,22 +2120,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>263</v>
+        <v>146</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>42</v>
@@ -4357,27 +2147,27 @@
         <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>42</v>
@@ -4389,27 +2179,27 @@
         <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>271</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>155</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>42</v>
@@ -4421,27 +2211,27 @@
         <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>274</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>42</v>
@@ -4453,27 +2243,27 @@
         <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>280</v>
+        <v>163</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>42</v>
@@ -4485,27 +2275,27 @@
         <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>165</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>42</v>
@@ -4517,27 +2307,27 @@
         <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>283</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>284</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>42</v>
@@ -4549,7 +2339,7 @@
         <v>42</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>285</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4584,37 +2374,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>286</v>
+        <v>169</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>287</v>
+        <v>170</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>288</v>
+        <v>171</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>289</v>
+        <v>172</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>290</v>
+        <v>173</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>291</v>
+        <v>174</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>292</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4622,34 +2412,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3">
         <v>168</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>294</v>
+        <v>177</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>296</v>
+        <v>179</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4657,34 +2447,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>189</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4692,34 +2482,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4727,34 +2517,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4762,34 +2552,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="C6" s="3">
         <v>192</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>301</v>
+        <v>184</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4797,34 +2587,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="C7" s="3">
         <v>164</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4838,28 +2628,28 @@
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>306</v>
+        <v>189</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4867,34 +2657,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="C9" s="3">
         <v>148</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4908,28 +2698,28 @@
         <v>172</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>306</v>
+        <v>189</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4937,34 +2727,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3">
         <v>102</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4978,28 +2768,28 @@
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>311</v>
+        <v>194</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5007,34 +2797,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3">
         <v>128</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5042,34 +2832,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>311</v>
+        <v>194</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5077,34 +2867,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3">
         <v>192</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5112,34 +2902,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>314</v>
+        <v>197</v>
       </c>
       <c r="C16" s="3">
         <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>315</v>
+        <v>198</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>317</v>
+        <v>200</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5147,34 +2937,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3">
         <v>224</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>319</v>
+        <v>202</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5182,34 +2972,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="C18" s="3">
         <v>78</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>321</v>
+        <v>204</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>322</v>
+        <v>205</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>323</v>
+        <v>206</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5217,34 +3007,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="C19" s="3">
         <v>176</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5252,34 +3042,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3">
         <v>175</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>311</v>
+        <v>194</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5287,34 +3077,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3">
         <v>154</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>324</v>
+        <v>207</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5322,34 +3112,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="C22" s="3">
         <v>472</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>325</v>
+        <v>208</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5357,34 +3147,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3">
         <v>118</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5392,34 +3182,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="C24" s="3">
         <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>326</v>
+        <v>209</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5427,34 +3217,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="C25" s="3">
         <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/dido-y-eneas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="205">
   <si>
     <t>Migración métrica · Dido y Eneas</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -40,21 +40,6 @@
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
-  </si>
-  <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -164,7 +149,7 @@
     <t>Esquema de rima · 20 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|5f98abeb-2033-4a53-9707-17d68b216e1d|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -719,14 +704,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1078,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1122,31 +1106,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1165,65 +1124,65 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1248,228 +1207,228 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>48</v>
+      <c r="G3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>51</v>
+      <c r="G4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>55</v>
+      <c r="G5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>61</v>
+      <c r="G7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1503,555 +1462,555 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>35</v>
+      <c r="E1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>91</v>
+        <v>78</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>127</v>
+        <v>107</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>134</v>
+        <v>107</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>136</v>
+        <v>99</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2086,260 +2045,260 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>35</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="G3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>157</v>
+      <c r="G4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>168</v>
+        <v>156</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2372,39 +2331,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2412,34 +2371,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3">
         <v>168</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2447,34 +2406,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2482,34 +2441,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C4" s="3">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K4" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2517,34 +2476,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" s="3">
         <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2552,34 +2511,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C6" s="3">
         <v>192</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2587,34 +2546,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3">
         <v>164</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2622,34 +2581,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3">
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2657,34 +2616,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C9" s="3">
         <v>148</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2692,34 +2651,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3">
         <v>172</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2727,34 +2686,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3">
         <v>102</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2762,34 +2721,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
         <v>50</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2797,34 +2756,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3">
         <v>128</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2832,34 +2791,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2867,34 +2826,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3">
         <v>192</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2902,34 +2861,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C16" s="3">
         <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2937,34 +2896,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C17" s="3">
         <v>224</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2972,34 +2931,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C18" s="3">
         <v>78</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3007,34 +2966,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C19" s="3">
         <v>176</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3042,34 +3001,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3">
         <v>175</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3077,34 +3036,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C21" s="3">
         <v>154</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3112,34 +3071,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C22" s="3">
         <v>472</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3147,34 +3106,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C23" s="3">
         <v>118</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3182,34 +3141,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C24" s="3">
         <v>44</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3217,34 +3176,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C25" s="3">
         <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
   </sheetData>
